--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:15:22+00:00</t>
+    <t>2025-07-07T09:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:23:07+00:00</t>
+    <t>2025-07-07T09:24:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-create-hb1ac-profile/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:24:06+00:00</t>
+    <t>2025-07-07T15:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
   </si>
   <si>
     <t>Profil de la ressource Observation pour définir une Glycémie
-Ce profil permet de gérer 4 types d'indicateurs de glycémie:
+Ce profil permet de gérer 3 types d'indicateurs de glycémie:
 - le taux de glucose sanguin, mesuré en mg/dl
 - le taux de glucose interstitiel, mesuré en mg/dl
 - l’index de gestion de glycémie (IGG) qui procure une estimation de l’HbA1c également mesuré en %
